--- a/EXCEL/ASSIGNMENT 4.xlsx
+++ b/EXCEL/ASSIGNMENT 4.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3b20d8914b1e23ee/Desktop/EXCEL Assignment/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3b20d8914b1e23ee/Desktop/Bytecode/EXCEL/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{F41FA0E9-E1F4-48A1-9F37-559CE0236F1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B78435CE-74DB-41BE-9DBA-5B258D6FC38B}"/>
@@ -890,20 +890,8 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -917,10 +905,22 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1258,54 +1258,54 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:16" x14ac:dyDescent="0.35">
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="22"/>
-      <c r="G3" s="22"/>
-      <c r="H3" s="22"/>
-      <c r="I3" s="22"/>
-      <c r="J3" s="22"/>
-      <c r="K3" s="22"/>
-      <c r="L3" s="22"/>
-      <c r="M3" s="22"/>
-      <c r="N3" s="22"/>
-      <c r="O3" s="22"/>
-      <c r="P3" s="22"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
+      <c r="J3" s="24"/>
+      <c r="K3" s="24"/>
+      <c r="L3" s="24"/>
+      <c r="M3" s="24"/>
+      <c r="N3" s="24"/>
+      <c r="O3" s="24"/>
+      <c r="P3" s="24"/>
     </row>
     <row r="4" spans="3:16" x14ac:dyDescent="0.35">
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22"/>
-      <c r="H4" s="22"/>
-      <c r="I4" s="22"/>
-      <c r="J4" s="22"/>
-      <c r="K4" s="22"/>
-      <c r="L4" s="22"/>
-      <c r="M4" s="22"/>
-      <c r="N4" s="22"/>
-      <c r="O4" s="22"/>
-      <c r="P4" s="22"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
+      <c r="I4" s="24"/>
+      <c r="J4" s="24"/>
+      <c r="K4" s="24"/>
+      <c r="L4" s="24"/>
+      <c r="M4" s="24"/>
+      <c r="N4" s="24"/>
+      <c r="O4" s="24"/>
+      <c r="P4" s="24"/>
     </row>
     <row r="5" spans="3:16" x14ac:dyDescent="0.35">
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="22"/>
-      <c r="G5" s="22"/>
-      <c r="H5" s="22"/>
-      <c r="I5" s="22"/>
-      <c r="J5" s="22"/>
-      <c r="K5" s="22"/>
-      <c r="L5" s="22"/>
-      <c r="M5" s="22"/>
-      <c r="N5" s="22"/>
-      <c r="O5" s="22"/>
-      <c r="P5" s="22"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="24"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="24"/>
+      <c r="K5" s="24"/>
+      <c r="L5" s="24"/>
+      <c r="M5" s="24"/>
+      <c r="N5" s="24"/>
+      <c r="O5" s="24"/>
+      <c r="P5" s="24"/>
     </row>
     <row r="6" spans="3:16" x14ac:dyDescent="0.35">
       <c r="D6" s="2"/>
@@ -1323,30 +1323,30 @@
       <c r="P6" s="2"/>
     </row>
     <row r="7" spans="3:16" x14ac:dyDescent="0.35">
-      <c r="E7" s="21" t="s">
+      <c r="E7" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="F7" s="21"/>
-      <c r="G7" s="21"/>
-      <c r="H7" s="21"/>
-      <c r="I7" s="21"/>
-      <c r="J7" s="21"/>
-      <c r="K7" s="21"/>
-      <c r="L7" s="21"/>
-      <c r="M7" s="21"/>
-      <c r="N7" s="21"/>
+      <c r="F7" s="23"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="23"/>
+      <c r="I7" s="23"/>
+      <c r="J7" s="23"/>
+      <c r="K7" s="23"/>
+      <c r="L7" s="23"/>
+      <c r="M7" s="23"/>
+      <c r="N7" s="23"/>
     </row>
     <row r="8" spans="3:16" x14ac:dyDescent="0.35">
-      <c r="E8" s="21"/>
-      <c r="F8" s="21"/>
-      <c r="G8" s="21"/>
-      <c r="H8" s="21"/>
-      <c r="I8" s="21"/>
-      <c r="J8" s="21"/>
-      <c r="K8" s="21"/>
-      <c r="L8" s="21"/>
-      <c r="M8" s="21"/>
-      <c r="N8" s="21"/>
+      <c r="E8" s="23"/>
+      <c r="F8" s="23"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="23"/>
+      <c r="I8" s="23"/>
+      <c r="J8" s="23"/>
+      <c r="K8" s="23"/>
+      <c r="L8" s="23"/>
+      <c r="M8" s="23"/>
+      <c r="N8" s="23"/>
     </row>
     <row r="10" spans="3:16" ht="38.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E10" s="5" t="s">
@@ -5282,73 +5282,73 @@
   </cols>
   <sheetData>
     <row r="4" spans="3:16" x14ac:dyDescent="0.35">
-      <c r="C4" s="23" t="s">
+      <c r="C4" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
-      <c r="G4" s="23"/>
-      <c r="H4" s="23"/>
-      <c r="I4" s="23"/>
-      <c r="J4" s="23"/>
-      <c r="K4" s="23"/>
-      <c r="L4" s="23"/>
-      <c r="M4" s="23"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="19"/>
+      <c r="M4" s="19"/>
     </row>
     <row r="5" spans="3:16" x14ac:dyDescent="0.35">
-      <c r="C5" s="23"/>
-      <c r="D5" s="23"/>
-      <c r="E5" s="23"/>
-      <c r="F5" s="23"/>
-      <c r="G5" s="23"/>
-      <c r="H5" s="23"/>
-      <c r="I5" s="23"/>
-      <c r="J5" s="23"/>
-      <c r="K5" s="23"/>
-      <c r="L5" s="23"/>
-      <c r="M5" s="23"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="19"/>
+      <c r="H5" s="19"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="19"/>
+      <c r="K5" s="19"/>
+      <c r="L5" s="19"/>
+      <c r="M5" s="19"/>
     </row>
     <row r="7" spans="3:16" x14ac:dyDescent="0.35">
-      <c r="C7" s="24" t="s">
+      <c r="C7" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="25"/>
-      <c r="G7" s="25"/>
-      <c r="H7" s="25"/>
-      <c r="I7" s="25"/>
-      <c r="J7" s="25"/>
-      <c r="K7" s="25"/>
-      <c r="L7" s="25"/>
-      <c r="M7" s="25"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="21"/>
+      <c r="F7" s="21"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="21"/>
+      <c r="I7" s="21"/>
+      <c r="J7" s="21"/>
+      <c r="K7" s="21"/>
+      <c r="L7" s="21"/>
+      <c r="M7" s="21"/>
     </row>
     <row r="8" spans="3:16" x14ac:dyDescent="0.35">
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="25"/>
-      <c r="I8" s="25"/>
-      <c r="J8" s="25"/>
-      <c r="K8" s="25"/>
-      <c r="L8" s="25"/>
-      <c r="M8" s="25"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="21"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="21"/>
+      <c r="I8" s="21"/>
+      <c r="J8" s="21"/>
+      <c r="K8" s="21"/>
+      <c r="L8" s="21"/>
+      <c r="M8" s="21"/>
     </row>
     <row r="9" spans="3:16" x14ac:dyDescent="0.35">
-      <c r="C9" s="25"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
-      <c r="F9" s="25"/>
-      <c r="G9" s="25"/>
-      <c r="H9" s="25"/>
-      <c r="I9" s="25"/>
-      <c r="J9" s="25"/>
-      <c r="K9" s="25"/>
-      <c r="L9" s="25"/>
-      <c r="M9" s="25"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="21"/>
+      <c r="I9" s="21"/>
+      <c r="J9" s="21"/>
+      <c r="K9" s="21"/>
+      <c r="L9" s="21"/>
+      <c r="M9" s="21"/>
     </row>
     <row r="11" spans="3:16" x14ac:dyDescent="0.35">
       <c r="C11" t="s">
@@ -6052,10 +6052,10 @@
       <c r="J32" t="s">
         <v>123</v>
       </c>
-      <c r="K32" s="26" t="s">
+      <c r="K32" s="22" t="s">
         <v>160</v>
       </c>
-      <c r="L32" s="26"/>
+      <c r="L32" s="22"/>
       <c r="N32" t="s">
         <v>113</v>
       </c>
@@ -6351,11 +6351,11 @@
       </c>
     </row>
     <row r="43" spans="3:18" x14ac:dyDescent="0.35">
-      <c r="D43" s="26" t="s">
+      <c r="D43" s="22" t="s">
         <v>160</v>
       </c>
-      <c r="E43" s="26"/>
-      <c r="F43" s="26"/>
+      <c r="E43" s="22"/>
+      <c r="F43" s="22"/>
     </row>
     <row r="44" spans="3:18" x14ac:dyDescent="0.35">
       <c r="C44" t="s">
@@ -6432,10 +6432,10 @@
       <c r="F48" t="s">
         <v>60</v>
       </c>
-      <c r="J48" s="28"/>
+      <c r="J48" s="18"/>
     </row>
     <row r="51" spans="9:9" ht="21" x14ac:dyDescent="0.5">
-      <c r="I51" s="28" t="s">
+      <c r="I51" s="18" t="s">
         <v>184</v>
       </c>
     </row>
@@ -6468,14 +6468,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
@@ -6664,12 +6664,12 @@
       </c>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="18"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="25"/>
       <c r="H9" t="s">
         <v>24</v>
       </c>
@@ -6717,12 +6717,12 @@
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
-      <c r="G12" s="19"/>
+      <c r="E12" s="26"/>
+      <c r="F12" s="26"/>
+      <c r="G12" s="26"/>
       <c r="H12" t="s">
         <v>25</v>
       </c>
@@ -6825,10 +6825,10 @@
         <v>40</v>
       </c>
       <c r="J3" s="3"/>
-      <c r="L3" s="27" t="s">
+      <c r="L3" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="M3" s="27"/>
+      <c r="M3" s="28"/>
     </row>
     <row r="4" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C4" cm="1">
